--- a/DesignerConfigs/Datas/Prop.xlsx
+++ b/DesignerConfigs/Datas/Prop.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
   <si>
     <t>##var</t>
   </si>
@@ -71,10 +71,13 @@
     <t>介绍</t>
   </si>
   <si>
-    <t>Sprites/UI/FuncIcon/LFuncIcon_Prop1.png</t>
-  </si>
-  <si>
-    <t>Sprites/UI/FuncIcon/LFuncIcon_Prop2.png</t>
+    <t>UI/FuncIcon/LFuncIcon_Prop1.png</t>
+  </si>
+  <si>
+    <t>UI/FuncIcon/LFuncIcon_Prop2.png</t>
+  </si>
+  <si>
+    <t>UI/FuncIcon/LFuncIcon_Prop3.png</t>
   </si>
 </sst>
 </file>
@@ -1142,34 +1145,45 @@
     <row r="6" ht="14.25" spans="1:5">
       <c r="A6" s="2"/>
       <c r="B6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>10224</v>
+        <v>10015</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
       </c>
       <c r="E6">
-        <v>10225</v>
+        <v>10016</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="B7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>10226</v>
+        <v>10017</v>
       </c>
       <c r="D7" t="s">
         <v>15</v>
       </c>
       <c r="E7">
-        <v>10227</v>
+        <v>10018</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="E8" s="3"/>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>10019</v>
+      </c>
+      <c r="D8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="3">
+        <v>10020</v>
+      </c>
     </row>
     <row r="26" spans="3:5">
       <c r="C26" s="4"/>

--- a/DesignerConfigs/Datas/Prop.xlsx
+++ b/DesignerConfigs/Datas/Prop.xlsx
@@ -1148,13 +1148,13 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>10015</v>
+        <v>10027</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
       </c>
       <c r="E6">
-        <v>10016</v>
+        <v>10028</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1162,13 +1162,13 @@
         <v>1</v>
       </c>
       <c r="C7">
-        <v>10017</v>
+        <v>10029</v>
       </c>
       <c r="D7" t="s">
         <v>15</v>
       </c>
       <c r="E7">
-        <v>10018</v>
+        <v>10030</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1176,13 +1176,13 @@
         <v>2</v>
       </c>
       <c r="C8">
-        <v>10019</v>
+        <v>10031</v>
       </c>
       <c r="D8" t="s">
         <v>16</v>
       </c>
       <c r="E8" s="3">
-        <v>10020</v>
+        <v>10032</v>
       </c>
     </row>
     <row r="26" spans="3:5">
